--- a/src/src/main/webapp/portal/budget/TemporallyPurchase/excel/Budget_Import_Template.xlsx
+++ b/src/src/main/webapp/portal/budget/TemporallyPurchase/excel/Budget_Import_Template.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503277717\Desktop\模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\budget\TemporallyPurchase\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44E9169-3955-48FC-AA8F-11FD0CEA8191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BFCD16-8F64-456F-BE9A-33C639CAC6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Budget List" sheetId="1" r:id="rId1"/>
+    <sheet name="Org List" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$2:$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Budget List'!$C$2:$C$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
   <si>
     <t>申请编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -237,16 +238,24 @@
   </si>
   <si>
     <t>否</t>
+  </si>
+  <si>
+    <t>部门名称</t>
+  </si>
+  <si>
+    <t>部门列表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,16 +284,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.499984740745262"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线 Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -351,11 +389,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -374,6 +427,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -392,8 +448,22 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -407,6 +477,195 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133349</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Inventory List" descr="Select to view Inventory List">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3CF7114-35FD-4990-8587-8DB34C7B18B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="19049" y="527685"/>
+          <a:ext cx="1725930" cy="203835"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="threePt" dir="t">
+            <a:rot lat="0" lon="0" rev="1200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>设备列表</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fPrintsWithSheet="0"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3809</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Inventory List" descr="Select to view Inventory List">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Click to view the Warehouse Inventory List"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E357C0F0-352F-4B6B-99C0-632052179D36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="19049" y="527685"/>
+          <a:ext cx="1725930" cy="203835"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="threePt" dir="t">
+            <a:rot lat="0" lon="0" rev="1200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>申购单列表</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fPrintsWithSheet="0"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -707,94 +966,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <dimension ref="A1:AP3"/>
-  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="14.1" outlineLevelCol="1" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="3" width="8.47265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.37890625" style="2" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="7" width="20.33203125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="10" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.6171875" customWidth="1"/>
-    <col min="13" max="13" width="7.6171875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="7.6171875" customWidth="1"/>
-    <col min="15" max="15" width="8.47265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="8.44921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.3984375" style="2" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="20.34765625" style="9" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="7" width="20.34765625" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="10" width="8.44921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.59765625" customWidth="1"/>
+    <col min="13" max="13" width="7.59765625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.59765625" customWidth="1"/>
+    <col min="15" max="15" width="8.44921875" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.94921875" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.37890625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.37890625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="32.234375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="48.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.37890625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.47265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.37890625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.37890625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.37890625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.37890625" customWidth="1"/>
-    <col min="33" max="33" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.37890625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="20.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="37" max="39" width="8.6171875" customWidth="1"/>
-    <col min="40" max="41" width="8.6171875" style="3" customWidth="1"/>
-    <col min="42" max="42" width="8.6171875" customWidth="1"/>
+    <col min="17" max="17" width="20.34765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.34765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.34765625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="48.1484375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.44921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.44921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.3984375" customWidth="1"/>
+    <col min="33" max="33" width="26.296875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.44921875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="20.34765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="37" max="39" width="8.59765625" customWidth="1"/>
+    <col min="40" max="41" width="8.59765625" style="3" customWidth="1"/>
+    <col min="42" max="42" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="7" customFormat="1" ht="17.7" thickBot="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:42" s="7" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="10" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-      <c r="AH1" s="11"/>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="10" t="s">
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AK1" s="11"/>
-      <c r="AL1" s="11"/>
-      <c r="AM1" s="11"/>
-      <c r="AN1" s="11"/>
-      <c r="AO1" s="11"/>
-      <c r="AP1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="12"/>
+      <c r="AN1" s="12"/>
+      <c r="AO1" s="12"/>
+      <c r="AP1" s="13"/>
     </row>
-    <row r="2" spans="1:42" s="1" customFormat="1" ht="28.5" customHeight="1">
+    <row r="2" spans="1:42" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -922,7 +1181,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.5">
       <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
@@ -1008,4 +1267,39 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28AF678-EA48-419A-9D5A-0C8C6DFB1620}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9.6484375" defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="22.84765625" style="17" customWidth="1"/>
+    <col min="2" max="16384" width="9.6484375" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A1" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A2" s="18"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A3" s="19"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A4" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To clear the pick list table in this worksheet, activate the object in B2 or press ALT+F8 and type &quot;ClearPickList&quot; with no spaces, then select RUN" sqref="A2" xr:uid="{0C95C331-93C2-4570-B0C6-CA5B0FD9B176}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>